--- a/data/Conditions_Queries.xlsx
+++ b/data/Conditions_Queries.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GIS\Henrico\Henrico_Data_2026\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D5DF2DD-5AA1-4A54-BBFA-37B7CB63FEB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{773DD919-EAC2-489B-A162-B5470833AF0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" activeTab="1" xr2:uid="{35C825B9-898A-46C9-A18E-DC972BBDF846}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{35C825B9-898A-46C9-A18E-DC972BBDF846}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -4671,27 +4671,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ed0ff079-217a-47d4-b7ec-91b316da1e03">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="3042e918-aefc-4171-9d6c-c740f3c2ff7c" xsi:nil="true"/>
-    <Status xmlns="ed0ff079-217a-47d4-b7ec-91b316da1e03" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101001F1BD6F70B794D4A83A1A74C1C7FFB13" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a36ec311cb1a64ba9887f4cfe263bcf0">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="ed0ff079-217a-47d4-b7ec-91b316da1e03" xmlns:ns3="3042e918-aefc-4171-9d6c-c740f3c2ff7c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b5d2f1e144e455241c9e34cacdc13afb" ns2:_="" ns3:_="">
     <xsd:import namespace="ed0ff079-217a-47d4-b7ec-91b316da1e03"/>
@@ -4934,10 +4913,42 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ed0ff079-217a-47d4-b7ec-91b316da1e03">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3042e918-aefc-4171-9d6c-c740f3c2ff7c" xsi:nil="true"/>
+    <Status xmlns="ed0ff079-217a-47d4-b7ec-91b316da1e03" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0627FB08-4574-4A0A-A2C4-FFFB20FF76D4}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F2AA363C-5FFF-4389-992E-0B1456F9F257}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="ed0ff079-217a-47d4-b7ec-91b316da1e03"/>
+    <ds:schemaRef ds:uri="3042e918-aefc-4171-9d6c-c740f3c2ff7c"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -4960,20 +4971,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F2AA363C-5FFF-4389-992E-0B1456F9F257}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0627FB08-4574-4A0A-A2C4-FFFB20FF76D4}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="ed0ff079-217a-47d4-b7ec-91b316da1e03"/>
-    <ds:schemaRef ds:uri="3042e918-aefc-4171-9d6c-c740f3c2ff7c"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/data/Conditions_Queries.xlsx
+++ b/data/Conditions_Queries.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GIS\Henrico\Henrico_Data_2026\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{773DD919-EAC2-489B-A162-B5470833AF0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C53C885-3800-4FE2-A450-0562617A0C06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{35C825B9-898A-46C9-A18E-DC972BBDF846}"/>
   </bookViews>
@@ -571,7 +571,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -623,14 +623,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <strike/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <strike/>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -646,14 +638,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <strike/>
-      <sz val="14"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <strike/>
       <sz val="11"/>
       <color theme="1"/>
@@ -663,9 +647,7 @@
     </font>
     <font>
       <b/>
-      <strike/>
-      <sz val="12"/>
-      <color theme="1"/>
+      <sz val="14"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1258,7 +1240,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="138">
+  <cellXfs count="139">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
@@ -1362,19 +1344,13 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="8" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="8" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1407,54 +1383,65 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="9" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="0" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="11" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="11" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="11" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="11" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="11" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -3467,17 +3454,17 @@
   <cols>
     <col min="1" max="1" width="112.42578125" customWidth="1"/>
     <col min="2" max="2" width="25.28515625" customWidth="1"/>
-    <col min="3" max="3" width="22.42578125" style="105" customWidth="1"/>
+    <col min="3" max="3" width="22.42578125" style="99" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" s="39" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="99" t="s">
+      <c r="A1" s="93" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="100" t="s">
+      <c r="B1" s="94" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="101" t="s">
+      <c r="C1" s="95" t="s">
         <v>2</v>
       </c>
     </row>
@@ -3485,10 +3472,8 @@
       <c r="A2" s="84" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="85">
-        <v>124287</v>
-      </c>
-      <c r="C2" s="107" t="s">
+      <c r="B2" s="85"/>
+      <c r="C2" s="101" t="s">
         <v>5</v>
       </c>
     </row>
@@ -3496,33 +3481,27 @@
       <c r="A3" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="81">
-        <v>177042</v>
-      </c>
-      <c r="C3" s="106"/>
+      <c r="B3" s="81"/>
+      <c r="C3" s="100"/>
     </row>
     <row r="4" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="82" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="83">
-        <v>113293</v>
-      </c>
-      <c r="C4" s="109"/>
+      <c r="B4" s="83"/>
+      <c r="C4" s="103"/>
     </row>
     <row r="5" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="41"/>
       <c r="B5" s="42"/>
-      <c r="C5" s="108"/>
+      <c r="C5" s="102"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="84" t="s">
         <v>59</v>
       </c>
-      <c r="B6" s="85">
-        <v>117556</v>
-      </c>
-      <c r="C6" s="107" t="s">
+      <c r="B6" s="85"/>
+      <c r="C6" s="101" t="s">
         <v>8</v>
       </c>
     </row>
@@ -3530,33 +3509,27 @@
       <c r="A7" s="87" t="s">
         <v>65</v>
       </c>
-      <c r="B7" s="88">
-        <v>175486</v>
-      </c>
-      <c r="C7" s="102"/>
+      <c r="B7" s="88"/>
+      <c r="C7" s="96"/>
     </row>
     <row r="8" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="90" t="s">
         <v>66</v>
       </c>
-      <c r="B8" s="91">
-        <v>112474</v>
-      </c>
-      <c r="C8" s="103"/>
+      <c r="B8" s="91"/>
+      <c r="C8" s="97"/>
     </row>
     <row r="9" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="41"/>
       <c r="B9" s="42"/>
-      <c r="C9" s="108"/>
+      <c r="C9" s="102"/>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="84" t="s">
         <v>67</v>
       </c>
-      <c r="B10" s="85">
-        <v>110246</v>
-      </c>
-      <c r="C10" s="107" t="s">
+      <c r="B10" s="85"/>
+      <c r="C10" s="101" t="s">
         <v>5</v>
       </c>
     </row>
@@ -3564,33 +3537,27 @@
       <c r="A11" s="87" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="88">
-        <v>173136</v>
-      </c>
-      <c r="C11" s="102"/>
+      <c r="B11" s="88"/>
+      <c r="C11" s="96"/>
     </row>
     <row r="12" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="90" t="s">
         <v>10</v>
       </c>
-      <c r="B12" s="91">
-        <v>111178</v>
-      </c>
-      <c r="C12" s="103"/>
+      <c r="B12" s="91"/>
+      <c r="C12" s="97"/>
     </row>
     <row r="13" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="41"/>
       <c r="B13" s="42"/>
-      <c r="C13" s="108"/>
+      <c r="C13" s="102"/>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="84" t="s">
         <v>108</v>
       </c>
-      <c r="B14" s="85">
-        <v>116359</v>
-      </c>
-      <c r="C14" s="107" t="s">
+      <c r="B14" s="85"/>
+      <c r="C14" s="101" t="s">
         <v>5</v>
       </c>
     </row>
@@ -3598,33 +3565,27 @@
       <c r="A15" s="87" t="s">
         <v>109</v>
       </c>
-      <c r="B15" s="88">
-        <v>174787</v>
-      </c>
-      <c r="C15" s="102"/>
+      <c r="B15" s="88"/>
+      <c r="C15" s="96"/>
     </row>
     <row r="16" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="90" t="s">
         <v>110</v>
       </c>
-      <c r="B16" s="91">
-        <v>112002</v>
-      </c>
-      <c r="C16" s="103"/>
+      <c r="B16" s="91"/>
+      <c r="C16" s="97"/>
     </row>
     <row r="17" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="41"/>
       <c r="B17" s="42"/>
-      <c r="C17" s="108"/>
+      <c r="C17" s="102"/>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="84" t="s">
         <v>70</v>
       </c>
-      <c r="B18" s="85">
-        <v>6732</v>
-      </c>
-      <c r="C18" s="107" t="s">
+      <c r="B18" s="85"/>
+      <c r="C18" s="101" t="s">
         <v>8</v>
       </c>
     </row>
@@ -3632,33 +3593,27 @@
       <c r="A19" s="87" t="s">
         <v>11</v>
       </c>
-      <c r="B19" s="88">
-        <v>1674</v>
-      </c>
-      <c r="C19" s="102"/>
+      <c r="B19" s="88"/>
+      <c r="C19" s="96"/>
     </row>
     <row r="20" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="90" t="s">
         <v>12</v>
       </c>
-      <c r="B20" s="91">
-        <v>841</v>
-      </c>
-      <c r="C20" s="103"/>
+      <c r="B20" s="91"/>
+      <c r="C20" s="97"/>
     </row>
     <row r="21" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="41"/>
       <c r="B21" s="42"/>
-      <c r="C21" s="108"/>
+      <c r="C21" s="102"/>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="84" t="s">
         <v>13</v>
       </c>
-      <c r="B22" s="85">
-        <v>7929</v>
-      </c>
-      <c r="C22" s="107" t="s">
+      <c r="B22" s="85"/>
+      <c r="C22" s="101" t="s">
         <v>5</v>
       </c>
     </row>
@@ -3666,33 +3621,27 @@
       <c r="A23" s="87" t="s">
         <v>14</v>
       </c>
-      <c r="B23" s="88">
-        <v>2373</v>
-      </c>
-      <c r="C23" s="102"/>
+      <c r="B23" s="88"/>
+      <c r="C23" s="96"/>
     </row>
     <row r="24" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="90" t="s">
         <v>15</v>
       </c>
-      <c r="B24" s="91">
-        <v>1313</v>
-      </c>
-      <c r="C24" s="103"/>
+      <c r="B24" s="91"/>
+      <c r="C24" s="97"/>
     </row>
     <row r="25" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="41"/>
       <c r="B25" s="46"/>
-      <c r="C25" s="108"/>
+      <c r="C25" s="102"/>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="84" t="s">
         <v>77</v>
       </c>
-      <c r="B26" s="85">
-        <v>14042</v>
-      </c>
-      <c r="C26" s="107" t="s">
+      <c r="B26" s="85"/>
+      <c r="C26" s="101" t="s">
         <v>8</v>
       </c>
     </row>
@@ -3700,33 +3649,27 @@
       <c r="A27" s="87" t="s">
         <v>78</v>
       </c>
-      <c r="B27" s="88">
-        <v>4024</v>
-      </c>
-      <c r="C27" s="102"/>
+      <c r="B27" s="88"/>
+      <c r="C27" s="96"/>
     </row>
     <row r="28" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="90" t="s">
         <v>79</v>
       </c>
-      <c r="B28" s="91">
-        <v>2137</v>
-      </c>
-      <c r="C28" s="103"/>
+      <c r="B28" s="91"/>
+      <c r="C28" s="97"/>
     </row>
     <row r="29" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="64"/>
       <c r="B29" s="42"/>
-      <c r="C29" s="108"/>
+      <c r="C29" s="102"/>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="84" t="s">
         <v>80</v>
       </c>
-      <c r="B30" s="85">
-        <v>619</v>
-      </c>
-      <c r="C30" s="107" t="s">
+      <c r="B30" s="85"/>
+      <c r="C30" s="101" t="s">
         <v>8</v>
       </c>
     </row>
@@ -3734,33 +3677,27 @@
       <c r="A31" s="87" t="s">
         <v>169</v>
       </c>
-      <c r="B31" s="88">
-        <v>23</v>
-      </c>
-      <c r="C31" s="102"/>
+      <c r="B31" s="88"/>
+      <c r="C31" s="96"/>
     </row>
     <row r="32" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="90" t="s">
         <v>82</v>
       </c>
-      <c r="B32" s="91">
-        <v>17</v>
-      </c>
-      <c r="C32" s="103"/>
+      <c r="B32" s="91"/>
+      <c r="C32" s="97"/>
     </row>
     <row r="33" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="41"/>
       <c r="B33" s="60"/>
-      <c r="C33" s="110"/>
+      <c r="C33" s="104"/>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="84" t="s">
         <v>84</v>
       </c>
-      <c r="B34" s="85">
-        <v>7294</v>
-      </c>
-      <c r="C34" s="107" t="s">
+      <c r="B34" s="85"/>
+      <c r="C34" s="101" t="s">
         <v>16</v>
       </c>
     </row>
@@ -3768,10 +3705,8 @@
       <c r="A35" s="87" t="s">
         <v>87</v>
       </c>
-      <c r="B35" s="88">
-        <v>1912</v>
-      </c>
-      <c r="C35" s="102" t="s">
+      <c r="B35" s="88"/>
+      <c r="C35" s="96" t="s">
         <v>5</v>
       </c>
     </row>
@@ -3779,26 +3714,22 @@
       <c r="A36" s="90" t="s">
         <v>88</v>
       </c>
-      <c r="B36" s="91">
-        <v>1112</v>
-      </c>
-      <c r="C36" s="103" t="s">
+      <c r="B36" s="91"/>
+      <c r="C36" s="97" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="51"/>
       <c r="B37" s="52"/>
-      <c r="C37" s="111"/>
+      <c r="C37" s="105"/>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="84" t="s">
         <v>113</v>
       </c>
-      <c r="B38" s="85">
-        <v>3479</v>
-      </c>
-      <c r="C38" s="107" t="s">
+      <c r="B38" s="85"/>
+      <c r="C38" s="101" t="s">
         <v>5</v>
       </c>
     </row>
@@ -3806,61 +3737,55 @@
       <c r="A39" s="87" t="s">
         <v>91</v>
       </c>
-      <c r="B39" s="88">
-        <v>1689</v>
-      </c>
-      <c r="C39" s="102"/>
+      <c r="B39" s="88"/>
+      <c r="C39" s="96"/>
     </row>
     <row r="40" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="90" t="s">
         <v>92</v>
       </c>
-      <c r="B40" s="91">
-        <v>974</v>
-      </c>
-      <c r="C40" s="103"/>
+      <c r="B40" s="91"/>
+      <c r="C40" s="97"/>
     </row>
     <row r="41" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="51"/>
       <c r="B41" s="52"/>
-      <c r="C41" s="111"/>
+      <c r="C41" s="105"/>
     </row>
     <row r="42" spans="1:3" s="80" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="93" t="s">
+      <c r="A42" s="84" t="s">
         <v>93</v>
       </c>
-      <c r="B42" s="94"/>
-      <c r="C42" s="112" t="s">
+      <c r="B42" s="132"/>
+      <c r="C42" s="133" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="43" spans="1:3" s="80" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="95" t="s">
+      <c r="A43" s="87" t="s">
         <v>94</v>
       </c>
-      <c r="B43" s="96"/>
-      <c r="C43" s="113"/>
+      <c r="B43" s="134"/>
+      <c r="C43" s="135"/>
     </row>
     <row r="44" spans="1:3" s="80" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="97" t="s">
+      <c r="A44" s="90" t="s">
         <v>95</v>
       </c>
-      <c r="B44" s="98"/>
-      <c r="C44" s="114"/>
+      <c r="B44" s="136"/>
+      <c r="C44" s="137"/>
     </row>
     <row r="45" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="51"/>
       <c r="B45" s="52"/>
-      <c r="C45" s="111"/>
+      <c r="C45" s="105"/>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" s="84" t="s">
         <v>98</v>
       </c>
-      <c r="B46" s="86">
-        <v>673</v>
-      </c>
-      <c r="C46" s="107" t="s">
+      <c r="B46" s="86"/>
+      <c r="C46" s="101" t="s">
         <v>8</v>
       </c>
     </row>
@@ -3868,33 +3793,27 @@
       <c r="A47" s="87" t="s">
         <v>99</v>
       </c>
-      <c r="B47" s="89">
-        <v>466</v>
-      </c>
-      <c r="C47" s="102"/>
+      <c r="B47" s="89"/>
+      <c r="C47" s="96"/>
     </row>
     <row r="48" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="90" t="s">
         <v>100</v>
       </c>
-      <c r="B48" s="92">
-        <v>301</v>
-      </c>
-      <c r="C48" s="103"/>
+      <c r="B48" s="92"/>
+      <c r="C48" s="97"/>
     </row>
     <row r="49" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="51"/>
       <c r="B49" s="52"/>
-      <c r="C49" s="111"/>
+      <c r="C49" s="105"/>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="84" t="s">
         <v>103</v>
       </c>
-      <c r="B50" s="86">
-        <v>22</v>
-      </c>
-      <c r="C50" s="107" t="s">
+      <c r="B50" s="86"/>
+      <c r="C50" s="101" t="s">
         <v>8</v>
       </c>
     </row>
@@ -3902,33 +3821,27 @@
       <c r="A51" s="87" t="s">
         <v>104</v>
       </c>
-      <c r="B51" s="89">
-        <v>303</v>
-      </c>
-      <c r="C51" s="102"/>
+      <c r="B51" s="89"/>
+      <c r="C51" s="96"/>
     </row>
     <row r="52" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A52" s="90" t="s">
         <v>105</v>
       </c>
-      <c r="B52" s="92">
-        <v>80</v>
-      </c>
-      <c r="C52" s="103"/>
+      <c r="B52" s="92"/>
+      <c r="C52" s="97"/>
     </row>
     <row r="53" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="41"/>
       <c r="B53" s="42"/>
-      <c r="C53" s="108"/>
+      <c r="C53" s="102"/>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" s="84" t="s">
         <v>166</v>
       </c>
-      <c r="B54" s="85">
-        <v>457</v>
-      </c>
-      <c r="C54" s="107" t="s">
+      <c r="B54" s="85"/>
+      <c r="C54" s="101" t="s">
         <v>8</v>
       </c>
     </row>
@@ -3936,716 +3849,712 @@
       <c r="A55" s="87" t="s">
         <v>167</v>
       </c>
-      <c r="B55" s="88">
-        <v>20</v>
-      </c>
-      <c r="C55" s="102"/>
+      <c r="B55" s="88"/>
+      <c r="C55" s="96"/>
     </row>
     <row r="56" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A56" s="90" t="s">
         <v>168</v>
       </c>
-      <c r="B56" s="91">
-        <v>14</v>
-      </c>
-      <c r="C56" s="103"/>
+      <c r="B56" s="91"/>
+      <c r="C56" s="97"/>
     </row>
     <row r="57" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A57" s="51"/>
       <c r="B57" s="52"/>
-      <c r="C57" s="104"/>
+      <c r="C57" s="98"/>
     </row>
     <row r="58" spans="1:3" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A58" s="115" t="s">
+      <c r="A58" s="138" t="s">
         <v>17</v>
       </c>
-      <c r="B58" s="116"/>
-      <c r="C58" s="117"/>
-    </row>
-    <row r="59" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="118" t="s">
+      <c r="B58" s="106"/>
+      <c r="C58" s="107"/>
+    </row>
+    <row r="59" spans="1:3" s="114" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="111" t="s">
         <v>18</v>
       </c>
-      <c r="B59" s="116"/>
-      <c r="C59" s="117"/>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A60" s="93" t="s">
+      <c r="B59" s="112"/>
+      <c r="C59" s="113"/>
+    </row>
+    <row r="60" spans="1:3" s="114" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="84" t="s">
         <v>115</v>
       </c>
-      <c r="B60" s="119"/>
-      <c r="C60" s="120"/>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A61" s="95" t="s">
+      <c r="B60" s="115"/>
+      <c r="C60" s="116"/>
+    </row>
+    <row r="61" spans="1:3" s="114" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="87" t="s">
         <v>114</v>
       </c>
-      <c r="B61" s="121"/>
-      <c r="C61" s="122"/>
-    </row>
-    <row r="62" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="97" t="s">
+      <c r="B61" s="117"/>
+      <c r="C61" s="118"/>
+    </row>
+    <row r="62" spans="1:3" s="114" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="90" t="s">
         <v>116</v>
       </c>
-      <c r="B62" s="123"/>
-      <c r="C62" s="124"/>
-    </row>
-    <row r="63" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="125"/>
-      <c r="B63" s="126"/>
-      <c r="C63" s="127"/>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A64" s="93" t="s">
+      <c r="B62" s="119"/>
+      <c r="C62" s="120"/>
+    </row>
+    <row r="63" spans="1:3" s="114" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="41"/>
+      <c r="B63" s="121"/>
+      <c r="C63" s="122"/>
+    </row>
+    <row r="64" spans="1:3" s="114" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="84" t="s">
         <v>117</v>
       </c>
-      <c r="B64" s="119"/>
-      <c r="C64" s="120"/>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A65" s="95" t="s">
+      <c r="B64" s="115"/>
+      <c r="C64" s="116"/>
+    </row>
+    <row r="65" spans="1:3" s="114" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="87" t="s">
         <v>118</v>
       </c>
-      <c r="B65" s="121"/>
-      <c r="C65" s="122"/>
-    </row>
-    <row r="66" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="128" t="s">
+      <c r="B65" s="117"/>
+      <c r="C65" s="118"/>
+    </row>
+    <row r="66" spans="1:3" s="114" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="123" t="s">
         <v>119</v>
       </c>
-      <c r="B66" s="124"/>
-      <c r="C66" s="124"/>
-    </row>
-    <row r="67" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="125"/>
-      <c r="B67" s="126"/>
-      <c r="C67" s="127"/>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A68" s="93" t="s">
+      <c r="B66" s="120"/>
+      <c r="C66" s="120"/>
+    </row>
+    <row r="67" spans="1:3" s="114" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="41"/>
+      <c r="B67" s="121"/>
+      <c r="C67" s="122"/>
+    </row>
+    <row r="68" spans="1:3" s="114" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="84" t="s">
         <v>120</v>
       </c>
-      <c r="B68" s="119"/>
-      <c r="C68" s="120"/>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A69" s="95" t="s">
+      <c r="B68" s="115"/>
+      <c r="C68" s="116"/>
+    </row>
+    <row r="69" spans="1:3" s="114" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="87" t="s">
         <v>121</v>
       </c>
-      <c r="B69" s="121"/>
-      <c r="C69" s="122"/>
-    </row>
-    <row r="70" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="97" t="s">
+      <c r="B69" s="117"/>
+      <c r="C69" s="118"/>
+    </row>
+    <row r="70" spans="1:3" s="114" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A70" s="90" t="s">
         <v>122</v>
       </c>
-      <c r="B70" s="123"/>
-      <c r="C70" s="124"/>
-    </row>
-    <row r="71" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="129"/>
-      <c r="B71" s="130"/>
-      <c r="C71" s="131"/>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A72" s="132" t="s">
+      <c r="B70" s="119"/>
+      <c r="C70" s="120"/>
+    </row>
+    <row r="71" spans="1:3" s="114" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="124"/>
+      <c r="B71" s="125"/>
+      <c r="C71" s="126"/>
+    </row>
+    <row r="72" spans="1:3" s="114" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="127" t="s">
         <v>123</v>
       </c>
-      <c r="B72" s="133"/>
-      <c r="C72" s="134"/>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A73" s="95" t="s">
+      <c r="B72" s="128"/>
+      <c r="C72" s="129"/>
+    </row>
+    <row r="73" spans="1:3" s="114" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="87" t="s">
         <v>124</v>
       </c>
-      <c r="B73" s="121"/>
-      <c r="C73" s="122"/>
-    </row>
-    <row r="74" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="97" t="s">
+      <c r="B73" s="117"/>
+      <c r="C73" s="118"/>
+    </row>
+    <row r="74" spans="1:3" s="114" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A74" s="90" t="s">
         <v>125</v>
       </c>
-      <c r="B74" s="123"/>
-      <c r="C74" s="124"/>
+      <c r="B74" s="119"/>
+      <c r="C74" s="120"/>
     </row>
     <row r="75" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="125"/>
-      <c r="B75" s="126"/>
-      <c r="C75" s="127"/>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A76" s="93" t="s">
+      <c r="A75" s="108"/>
+      <c r="B75" s="109"/>
+      <c r="C75" s="110"/>
+    </row>
+    <row r="76" spans="1:3" s="114" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="84" t="s">
         <v>166</v>
       </c>
-      <c r="B76" s="119"/>
-      <c r="C76" s="120"/>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A77" s="95" t="s">
+      <c r="B76" s="115"/>
+      <c r="C76" s="116"/>
+    </row>
+    <row r="77" spans="1:3" s="114" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="87" t="s">
         <v>167</v>
       </c>
-      <c r="B77" s="121"/>
-      <c r="C77" s="122"/>
-    </row>
-    <row r="78" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="97" t="s">
+      <c r="B77" s="117"/>
+      <c r="C77" s="118"/>
+    </row>
+    <row r="78" spans="1:3" s="114" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A78" s="90" t="s">
         <v>168</v>
       </c>
-      <c r="B78" s="123"/>
-      <c r="C78" s="124"/>
-    </row>
-    <row r="79" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="135"/>
-      <c r="B79" s="136"/>
-      <c r="C79" s="137"/>
-    </row>
-    <row r="80" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="118" t="s">
+      <c r="B78" s="119"/>
+      <c r="C78" s="120"/>
+    </row>
+    <row r="79" spans="1:3" s="114" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A79" s="71"/>
+      <c r="B79" s="130"/>
+      <c r="C79" s="131"/>
+    </row>
+    <row r="80" spans="1:3" s="114" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A80" s="111" t="s">
         <v>19</v>
       </c>
-      <c r="B80" s="116"/>
-      <c r="C80" s="117"/>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A81" s="93" t="s">
+      <c r="B80" s="112"/>
+      <c r="C80" s="113"/>
+    </row>
+    <row r="81" spans="1:3" s="114" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A81" s="84" t="s">
         <v>115</v>
       </c>
-      <c r="B81" s="119"/>
-      <c r="C81" s="120"/>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A82" s="95" t="s">
+      <c r="B81" s="115"/>
+      <c r="C81" s="116"/>
+    </row>
+    <row r="82" spans="1:3" s="114" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="87" t="s">
         <v>114</v>
       </c>
-      <c r="B82" s="121"/>
-      <c r="C82" s="122"/>
-    </row>
-    <row r="83" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="97" t="s">
+      <c r="B82" s="117"/>
+      <c r="C82" s="118"/>
+    </row>
+    <row r="83" spans="1:3" s="114" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A83" s="90" t="s">
         <v>116</v>
       </c>
-      <c r="B83" s="123"/>
-      <c r="C83" s="124"/>
-    </row>
-    <row r="84" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="125"/>
-      <c r="B84" s="126"/>
-      <c r="C84" s="127"/>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A85" s="93" t="s">
+      <c r="B83" s="119"/>
+      <c r="C83" s="120"/>
+    </row>
+    <row r="84" spans="1:3" s="114" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A84" s="41"/>
+      <c r="B84" s="121"/>
+      <c r="C84" s="122"/>
+    </row>
+    <row r="85" spans="1:3" s="114" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A85" s="84" t="s">
         <v>117</v>
       </c>
-      <c r="B85" s="119"/>
-      <c r="C85" s="120"/>
-    </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A86" s="95" t="s">
+      <c r="B85" s="115"/>
+      <c r="C85" s="116"/>
+    </row>
+    <row r="86" spans="1:3" s="114" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A86" s="87" t="s">
         <v>118</v>
       </c>
-      <c r="B86" s="121"/>
-      <c r="C86" s="122"/>
-    </row>
-    <row r="87" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="128" t="s">
+      <c r="B86" s="117"/>
+      <c r="C86" s="118"/>
+    </row>
+    <row r="87" spans="1:3" s="114" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A87" s="123" t="s">
         <v>119</v>
       </c>
-      <c r="B87" s="124"/>
-      <c r="C87" s="124"/>
-    </row>
-    <row r="88" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="125"/>
-      <c r="B88" s="126"/>
-      <c r="C88" s="127"/>
-    </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A89" s="93" t="s">
+      <c r="B87" s="120"/>
+      <c r="C87" s="120"/>
+    </row>
+    <row r="88" spans="1:3" s="114" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A88" s="41"/>
+      <c r="B88" s="121"/>
+      <c r="C88" s="122"/>
+    </row>
+    <row r="89" spans="1:3" s="114" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A89" s="84" t="s">
         <v>120</v>
       </c>
-      <c r="B89" s="119"/>
-      <c r="C89" s="120"/>
-    </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A90" s="95" t="s">
+      <c r="B89" s="115"/>
+      <c r="C89" s="116"/>
+    </row>
+    <row r="90" spans="1:3" s="114" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A90" s="87" t="s">
         <v>121</v>
       </c>
-      <c r="B90" s="121"/>
-      <c r="C90" s="122"/>
-    </row>
-    <row r="91" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A91" s="97" t="s">
+      <c r="B90" s="117"/>
+      <c r="C90" s="118"/>
+    </row>
+    <row r="91" spans="1:3" s="114" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A91" s="90" t="s">
         <v>122</v>
       </c>
-      <c r="B91" s="123"/>
-      <c r="C91" s="124"/>
-    </row>
-    <row r="92" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="129"/>
-      <c r="B92" s="130"/>
-      <c r="C92" s="131"/>
-    </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A93" s="132" t="s">
+      <c r="B91" s="119"/>
+      <c r="C91" s="120"/>
+    </row>
+    <row r="92" spans="1:3" s="114" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A92" s="124"/>
+      <c r="B92" s="125"/>
+      <c r="C92" s="126"/>
+    </row>
+    <row r="93" spans="1:3" s="114" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A93" s="127" t="s">
         <v>123</v>
       </c>
-      <c r="B93" s="133"/>
-      <c r="C93" s="134"/>
-    </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A94" s="95" t="s">
+      <c r="B93" s="128"/>
+      <c r="C93" s="129"/>
+    </row>
+    <row r="94" spans="1:3" s="114" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A94" s="87" t="s">
         <v>124</v>
       </c>
-      <c r="B94" s="121"/>
-      <c r="C94" s="122"/>
-    </row>
-    <row r="95" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A95" s="97" t="s">
+      <c r="B94" s="117"/>
+      <c r="C94" s="118"/>
+    </row>
+    <row r="95" spans="1:3" s="114" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A95" s="90" t="s">
         <v>125</v>
       </c>
-      <c r="B95" s="123"/>
-      <c r="C95" s="124"/>
-    </row>
-    <row r="96" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="125"/>
-      <c r="B96" s="126"/>
-      <c r="C96" s="127"/>
-    </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A97" s="93" t="s">
+      <c r="B95" s="119"/>
+      <c r="C95" s="120"/>
+    </row>
+    <row r="96" spans="1:3" s="114" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A96" s="41"/>
+      <c r="B96" s="121"/>
+      <c r="C96" s="122"/>
+    </row>
+    <row r="97" spans="1:3" s="114" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A97" s="84" t="s">
         <v>166</v>
       </c>
-      <c r="B97" s="119"/>
-      <c r="C97" s="120"/>
-    </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A98" s="95" t="s">
+      <c r="B97" s="115"/>
+      <c r="C97" s="116"/>
+    </row>
+    <row r="98" spans="1:3" s="114" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A98" s="87" t="s">
         <v>167</v>
       </c>
-      <c r="B98" s="121"/>
-      <c r="C98" s="122"/>
-    </row>
-    <row r="99" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A99" s="97" t="s">
+      <c r="B98" s="117"/>
+      <c r="C98" s="118"/>
+    </row>
+    <row r="99" spans="1:3" s="114" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A99" s="90" t="s">
         <v>168</v>
       </c>
-      <c r="B99" s="123"/>
-      <c r="C99" s="124"/>
-    </row>
-    <row r="100" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A100" s="135"/>
-      <c r="B100" s="136"/>
-      <c r="C100" s="137"/>
-    </row>
-    <row r="101" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A101" s="118" t="s">
+      <c r="B99" s="119"/>
+      <c r="C99" s="120"/>
+    </row>
+    <row r="100" spans="1:3" s="114" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A100" s="71"/>
+      <c r="B100" s="130"/>
+      <c r="C100" s="131"/>
+    </row>
+    <row r="101" spans="1:3" s="114" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A101" s="111" t="s">
         <v>20</v>
       </c>
-      <c r="B101" s="116"/>
-      <c r="C101" s="117"/>
-    </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A102" s="93" t="s">
+      <c r="B101" s="112"/>
+      <c r="C101" s="113"/>
+    </row>
+    <row r="102" spans="1:3" s="114" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A102" s="84" t="s">
         <v>115</v>
       </c>
-      <c r="B102" s="119"/>
-      <c r="C102" s="120"/>
-    </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A103" s="95" t="s">
+      <c r="B102" s="115"/>
+      <c r="C102" s="116"/>
+    </row>
+    <row r="103" spans="1:3" s="114" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A103" s="87" t="s">
         <v>114</v>
       </c>
-      <c r="B103" s="121"/>
-      <c r="C103" s="122"/>
-    </row>
-    <row r="104" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A104" s="97" t="s">
+      <c r="B103" s="117"/>
+      <c r="C103" s="118"/>
+    </row>
+    <row r="104" spans="1:3" s="114" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A104" s="90" t="s">
         <v>116</v>
       </c>
-      <c r="B104" s="123"/>
-      <c r="C104" s="124"/>
-    </row>
-    <row r="105" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A105" s="125"/>
-      <c r="B105" s="126"/>
-      <c r="C105" s="127"/>
-    </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A106" s="93" t="s">
+      <c r="B104" s="119"/>
+      <c r="C104" s="120"/>
+    </row>
+    <row r="105" spans="1:3" s="114" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A105" s="41"/>
+      <c r="B105" s="121"/>
+      <c r="C105" s="122"/>
+    </row>
+    <row r="106" spans="1:3" s="114" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A106" s="84" t="s">
         <v>117</v>
       </c>
-      <c r="B106" s="119"/>
-      <c r="C106" s="120"/>
-    </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A107" s="95" t="s">
+      <c r="B106" s="115"/>
+      <c r="C106" s="116"/>
+    </row>
+    <row r="107" spans="1:3" s="114" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A107" s="87" t="s">
         <v>118</v>
       </c>
-      <c r="B107" s="121"/>
-      <c r="C107" s="122"/>
-    </row>
-    <row r="108" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A108" s="128" t="s">
+      <c r="B107" s="117"/>
+      <c r="C107" s="118"/>
+    </row>
+    <row r="108" spans="1:3" s="114" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A108" s="123" t="s">
         <v>119</v>
       </c>
-      <c r="B108" s="124"/>
-      <c r="C108" s="124"/>
-    </row>
-    <row r="109" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A109" s="125"/>
-      <c r="B109" s="126"/>
-      <c r="C109" s="127"/>
-    </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A110" s="93" t="s">
+      <c r="B108" s="120"/>
+      <c r="C108" s="120"/>
+    </row>
+    <row r="109" spans="1:3" s="114" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A109" s="41"/>
+      <c r="B109" s="121"/>
+      <c r="C109" s="122"/>
+    </row>
+    <row r="110" spans="1:3" s="114" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A110" s="84" t="s">
         <v>120</v>
       </c>
-      <c r="B110" s="119"/>
-      <c r="C110" s="120"/>
-    </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A111" s="95" t="s">
+      <c r="B110" s="115"/>
+      <c r="C110" s="116"/>
+    </row>
+    <row r="111" spans="1:3" s="114" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A111" s="87" t="s">
         <v>121</v>
       </c>
-      <c r="B111" s="121"/>
-      <c r="C111" s="122"/>
-    </row>
-    <row r="112" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A112" s="97" t="s">
+      <c r="B111" s="117"/>
+      <c r="C111" s="118"/>
+    </row>
+    <row r="112" spans="1:3" s="114" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A112" s="90" t="s">
         <v>122</v>
       </c>
-      <c r="B112" s="123"/>
-      <c r="C112" s="124"/>
-    </row>
-    <row r="113" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A113" s="129"/>
-      <c r="B113" s="130"/>
-      <c r="C113" s="131"/>
-    </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A114" s="132" t="s">
+      <c r="B112" s="119"/>
+      <c r="C112" s="120"/>
+    </row>
+    <row r="113" spans="1:3" s="114" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A113" s="124"/>
+      <c r="B113" s="125"/>
+      <c r="C113" s="126"/>
+    </row>
+    <row r="114" spans="1:3" s="114" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A114" s="127" t="s">
         <v>123</v>
       </c>
-      <c r="B114" s="133"/>
-      <c r="C114" s="134"/>
-    </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A115" s="95" t="s">
+      <c r="B114" s="128"/>
+      <c r="C114" s="129"/>
+    </row>
+    <row r="115" spans="1:3" s="114" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A115" s="87" t="s">
         <v>124</v>
       </c>
-      <c r="B115" s="121"/>
-      <c r="C115" s="122"/>
-    </row>
-    <row r="116" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A116" s="97" t="s">
+      <c r="B115" s="117"/>
+      <c r="C115" s="118"/>
+    </row>
+    <row r="116" spans="1:3" s="114" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A116" s="90" t="s">
         <v>125</v>
       </c>
-      <c r="B116" s="123"/>
-      <c r="C116" s="124"/>
-    </row>
-    <row r="117" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A117" s="125"/>
-      <c r="B117" s="126"/>
-      <c r="C117" s="127"/>
-    </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A118" s="93" t="s">
+      <c r="B116" s="119"/>
+      <c r="C116" s="120"/>
+    </row>
+    <row r="117" spans="1:3" s="114" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A117" s="41"/>
+      <c r="B117" s="121"/>
+      <c r="C117" s="122"/>
+    </row>
+    <row r="118" spans="1:3" s="114" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A118" s="84" t="s">
         <v>166</v>
       </c>
-      <c r="B118" s="119"/>
-      <c r="C118" s="120"/>
-    </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A119" s="95" t="s">
+      <c r="B118" s="115"/>
+      <c r="C118" s="116"/>
+    </row>
+    <row r="119" spans="1:3" s="114" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A119" s="87" t="s">
         <v>167</v>
       </c>
-      <c r="B119" s="121"/>
-      <c r="C119" s="122"/>
-    </row>
-    <row r="120" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A120" s="97" t="s">
+      <c r="B119" s="117"/>
+      <c r="C119" s="118"/>
+    </row>
+    <row r="120" spans="1:3" s="114" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A120" s="90" t="s">
         <v>168</v>
       </c>
-      <c r="B120" s="123"/>
-      <c r="C120" s="124"/>
-    </row>
-    <row r="121" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A121" s="135"/>
-      <c r="B121" s="136"/>
-      <c r="C121" s="137"/>
-    </row>
-    <row r="122" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A122" s="118" t="s">
+      <c r="B120" s="119"/>
+      <c r="C120" s="120"/>
+    </row>
+    <row r="121" spans="1:3" s="114" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A121" s="71"/>
+      <c r="B121" s="130"/>
+      <c r="C121" s="131"/>
+    </row>
+    <row r="122" spans="1:3" s="114" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A122" s="111" t="s">
         <v>21</v>
       </c>
-      <c r="B122" s="116"/>
-      <c r="C122" s="117"/>
-    </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A123" s="93" t="s">
+      <c r="B122" s="112"/>
+      <c r="C122" s="113"/>
+    </row>
+    <row r="123" spans="1:3" s="114" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A123" s="84" t="s">
         <v>115</v>
       </c>
-      <c r="B123" s="119"/>
-      <c r="C123" s="120"/>
-    </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A124" s="95" t="s">
+      <c r="B123" s="115"/>
+      <c r="C123" s="116"/>
+    </row>
+    <row r="124" spans="1:3" s="114" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A124" s="87" t="s">
         <v>114</v>
       </c>
-      <c r="B124" s="121"/>
-      <c r="C124" s="122"/>
-    </row>
-    <row r="125" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A125" s="97" t="s">
+      <c r="B124" s="117"/>
+      <c r="C124" s="118"/>
+    </row>
+    <row r="125" spans="1:3" s="114" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A125" s="90" t="s">
         <v>116</v>
       </c>
-      <c r="B125" s="123"/>
-      <c r="C125" s="124"/>
-    </row>
-    <row r="126" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A126" s="125"/>
-      <c r="B126" s="126"/>
-      <c r="C126" s="127"/>
-    </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A127" s="93" t="s">
+      <c r="B125" s="119"/>
+      <c r="C125" s="120"/>
+    </row>
+    <row r="126" spans="1:3" s="114" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A126" s="41"/>
+      <c r="B126" s="121"/>
+      <c r="C126" s="122"/>
+    </row>
+    <row r="127" spans="1:3" s="114" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A127" s="84" t="s">
         <v>117</v>
       </c>
-      <c r="B127" s="119"/>
-      <c r="C127" s="120"/>
-    </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A128" s="95" t="s">
+      <c r="B127" s="115"/>
+      <c r="C127" s="116"/>
+    </row>
+    <row r="128" spans="1:3" s="114" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A128" s="87" t="s">
         <v>118</v>
       </c>
-      <c r="B128" s="121"/>
-      <c r="C128" s="122"/>
-    </row>
-    <row r="129" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A129" s="128" t="s">
+      <c r="B128" s="117"/>
+      <c r="C128" s="118"/>
+    </row>
+    <row r="129" spans="1:3" s="114" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A129" s="123" t="s">
         <v>119</v>
       </c>
-      <c r="B129" s="124"/>
-      <c r="C129" s="124"/>
-    </row>
-    <row r="130" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A130" s="125"/>
-      <c r="B130" s="126"/>
-      <c r="C130" s="127"/>
-    </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A131" s="93" t="s">
+      <c r="B129" s="120"/>
+      <c r="C129" s="120"/>
+    </row>
+    <row r="130" spans="1:3" s="114" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A130" s="41"/>
+      <c r="B130" s="121"/>
+      <c r="C130" s="122"/>
+    </row>
+    <row r="131" spans="1:3" s="114" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A131" s="84" t="s">
         <v>120</v>
       </c>
-      <c r="B131" s="119"/>
-      <c r="C131" s="120"/>
-    </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A132" s="95" t="s">
+      <c r="B131" s="115"/>
+      <c r="C131" s="116"/>
+    </row>
+    <row r="132" spans="1:3" s="114" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A132" s="87" t="s">
         <v>121</v>
       </c>
-      <c r="B132" s="121"/>
-      <c r="C132" s="122"/>
-    </row>
-    <row r="133" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A133" s="97" t="s">
+      <c r="B132" s="117"/>
+      <c r="C132" s="118"/>
+    </row>
+    <row r="133" spans="1:3" s="114" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A133" s="90" t="s">
         <v>122</v>
       </c>
-      <c r="B133" s="123"/>
-      <c r="C133" s="124"/>
-    </row>
-    <row r="134" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A134" s="129"/>
-      <c r="B134" s="130"/>
-      <c r="C134" s="131"/>
-    </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A135" s="132" t="s">
+      <c r="B133" s="119"/>
+      <c r="C133" s="120"/>
+    </row>
+    <row r="134" spans="1:3" s="114" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A134" s="124"/>
+      <c r="B134" s="125"/>
+      <c r="C134" s="126"/>
+    </row>
+    <row r="135" spans="1:3" s="114" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A135" s="127" t="s">
         <v>123</v>
       </c>
-      <c r="B135" s="133"/>
-      <c r="C135" s="134"/>
-    </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A136" s="95" t="s">
+      <c r="B135" s="128"/>
+      <c r="C135" s="129"/>
+    </row>
+    <row r="136" spans="1:3" s="114" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A136" s="87" t="s">
         <v>124</v>
       </c>
-      <c r="B136" s="121"/>
-      <c r="C136" s="122"/>
-    </row>
-    <row r="137" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A137" s="97" t="s">
+      <c r="B136" s="117"/>
+      <c r="C136" s="118"/>
+    </row>
+    <row r="137" spans="1:3" s="114" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A137" s="90" t="s">
         <v>125</v>
       </c>
-      <c r="B137" s="123"/>
-      <c r="C137" s="124"/>
-    </row>
-    <row r="138" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A138" s="125"/>
-      <c r="B138" s="126"/>
-      <c r="C138" s="127"/>
-    </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A139" s="93" t="s">
+      <c r="B137" s="119"/>
+      <c r="C137" s="120"/>
+    </row>
+    <row r="138" spans="1:3" s="114" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A138" s="41"/>
+      <c r="B138" s="121"/>
+      <c r="C138" s="122"/>
+    </row>
+    <row r="139" spans="1:3" s="114" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A139" s="84" t="s">
         <v>166</v>
       </c>
-      <c r="B139" s="119"/>
-      <c r="C139" s="120"/>
-    </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A140" s="95" t="s">
+      <c r="B139" s="115"/>
+      <c r="C139" s="116"/>
+    </row>
+    <row r="140" spans="1:3" s="114" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A140" s="87" t="s">
         <v>167</v>
       </c>
-      <c r="B140" s="121"/>
-      <c r="C140" s="122"/>
-    </row>
-    <row r="141" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A141" s="97" t="s">
+      <c r="B140" s="117"/>
+      <c r="C140" s="118"/>
+    </row>
+    <row r="141" spans="1:3" s="114" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A141" s="90" t="s">
         <v>168</v>
       </c>
-      <c r="B141" s="123"/>
-      <c r="C141" s="124"/>
-    </row>
-    <row r="142" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A142" s="135"/>
-      <c r="B142" s="136"/>
-      <c r="C142" s="137"/>
-    </row>
-    <row r="143" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A143" s="118" t="s">
+      <c r="B141" s="119"/>
+      <c r="C141" s="120"/>
+    </row>
+    <row r="142" spans="1:3" s="114" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A142" s="71"/>
+      <c r="B142" s="130"/>
+      <c r="C142" s="131"/>
+    </row>
+    <row r="143" spans="1:3" s="114" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A143" s="111" t="s">
         <v>22</v>
       </c>
-      <c r="B143" s="116"/>
-      <c r="C143" s="117"/>
-    </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A144" s="93" t="s">
+      <c r="B143" s="112"/>
+      <c r="C143" s="113"/>
+    </row>
+    <row r="144" spans="1:3" s="114" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A144" s="84" t="s">
         <v>115</v>
       </c>
-      <c r="B144" s="119"/>
-      <c r="C144" s="120"/>
-    </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A145" s="95" t="s">
+      <c r="B144" s="115"/>
+      <c r="C144" s="116"/>
+    </row>
+    <row r="145" spans="1:3" s="114" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A145" s="87" t="s">
         <v>114</v>
       </c>
-      <c r="B145" s="121"/>
-      <c r="C145" s="122"/>
-    </row>
-    <row r="146" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A146" s="97" t="s">
+      <c r="B145" s="117"/>
+      <c r="C145" s="118"/>
+    </row>
+    <row r="146" spans="1:3" s="114" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A146" s="90" t="s">
         <v>116</v>
       </c>
-      <c r="B146" s="123"/>
-      <c r="C146" s="124"/>
-    </row>
-    <row r="147" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A147" s="125"/>
-      <c r="B147" s="126"/>
-      <c r="C147" s="127"/>
-    </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A148" s="93" t="s">
+      <c r="B146" s="119"/>
+      <c r="C146" s="120"/>
+    </row>
+    <row r="147" spans="1:3" s="114" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A147" s="41"/>
+      <c r="B147" s="121"/>
+      <c r="C147" s="122"/>
+    </row>
+    <row r="148" spans="1:3" s="114" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A148" s="84" t="s">
         <v>117</v>
       </c>
-      <c r="B148" s="119"/>
-      <c r="C148" s="120"/>
-    </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A149" s="95" t="s">
+      <c r="B148" s="115"/>
+      <c r="C148" s="116"/>
+    </row>
+    <row r="149" spans="1:3" s="114" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A149" s="87" t="s">
         <v>118</v>
       </c>
-      <c r="B149" s="121"/>
-      <c r="C149" s="122"/>
-    </row>
-    <row r="150" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A150" s="128" t="s">
+      <c r="B149" s="117"/>
+      <c r="C149" s="118"/>
+    </row>
+    <row r="150" spans="1:3" s="114" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A150" s="123" t="s">
         <v>119</v>
       </c>
-      <c r="B150" s="124"/>
-      <c r="C150" s="124"/>
-    </row>
-    <row r="151" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A151" s="125"/>
-      <c r="B151" s="126"/>
-      <c r="C151" s="127"/>
-    </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A152" s="93" t="s">
+      <c r="B150" s="120"/>
+      <c r="C150" s="120"/>
+    </row>
+    <row r="151" spans="1:3" s="114" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A151" s="41"/>
+      <c r="B151" s="121"/>
+      <c r="C151" s="122"/>
+    </row>
+    <row r="152" spans="1:3" s="114" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A152" s="84" t="s">
         <v>120</v>
       </c>
-      <c r="B152" s="119"/>
-      <c r="C152" s="120"/>
-    </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A153" s="95" t="s">
+      <c r="B152" s="115"/>
+      <c r="C152" s="116"/>
+    </row>
+    <row r="153" spans="1:3" s="114" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A153" s="87" t="s">
         <v>121</v>
       </c>
-      <c r="B153" s="121"/>
-      <c r="C153" s="122"/>
-    </row>
-    <row r="154" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A154" s="97" t="s">
+      <c r="B153" s="117"/>
+      <c r="C153" s="118"/>
+    </row>
+    <row r="154" spans="1:3" s="114" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A154" s="90" t="s">
         <v>122</v>
       </c>
-      <c r="B154" s="123"/>
-      <c r="C154" s="124"/>
-    </row>
-    <row r="155" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A155" s="129"/>
-      <c r="B155" s="130"/>
-      <c r="C155" s="131"/>
-    </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A156" s="132" t="s">
+      <c r="B154" s="119"/>
+      <c r="C154" s="120"/>
+    </row>
+    <row r="155" spans="1:3" s="114" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A155" s="124"/>
+      <c r="B155" s="125"/>
+      <c r="C155" s="126"/>
+    </row>
+    <row r="156" spans="1:3" s="114" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A156" s="127" t="s">
         <v>123</v>
       </c>
-      <c r="B156" s="133"/>
-      <c r="C156" s="134"/>
-    </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A157" s="95" t="s">
+      <c r="B156" s="128"/>
+      <c r="C156" s="129"/>
+    </row>
+    <row r="157" spans="1:3" s="114" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A157" s="87" t="s">
         <v>124</v>
       </c>
-      <c r="B157" s="121"/>
-      <c r="C157" s="122"/>
-    </row>
-    <row r="158" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A158" s="97" t="s">
+      <c r="B157" s="117"/>
+      <c r="C157" s="118"/>
+    </row>
+    <row r="158" spans="1:3" s="114" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A158" s="90" t="s">
         <v>125</v>
       </c>
-      <c r="B158" s="123"/>
-      <c r="C158" s="124"/>
-    </row>
-    <row r="159" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A159" s="125"/>
-      <c r="B159" s="126"/>
-      <c r="C159" s="127"/>
-    </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A160" s="93" t="s">
+      <c r="B158" s="119"/>
+      <c r="C158" s="120"/>
+    </row>
+    <row r="159" spans="1:3" s="114" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A159" s="41"/>
+      <c r="B159" s="121"/>
+      <c r="C159" s="122"/>
+    </row>
+    <row r="160" spans="1:3" s="114" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A160" s="84" t="s">
         <v>166</v>
       </c>
-      <c r="B160" s="119"/>
-      <c r="C160" s="120"/>
-    </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A161" s="95" t="s">
+      <c r="B160" s="115"/>
+      <c r="C160" s="116"/>
+    </row>
+    <row r="161" spans="1:3" s="114" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A161" s="87" t="s">
         <v>167</v>
       </c>
-      <c r="B161" s="121"/>
-      <c r="C161" s="122"/>
-    </row>
-    <row r="162" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A162" s="97" t="s">
+      <c r="B161" s="117"/>
+      <c r="C161" s="118"/>
+    </row>
+    <row r="162" spans="1:3" s="114" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A162" s="90" t="s">
         <v>168</v>
       </c>
-      <c r="B162" s="123"/>
-      <c r="C162" s="124"/>
-    </row>
-    <row r="163" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A163" s="135"/>
-      <c r="B163" s="136"/>
-      <c r="C163" s="137"/>
+      <c r="B162" s="119"/>
+      <c r="C162" s="120"/>
+    </row>
+    <row r="163" spans="1:3" s="114" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A163" s="71"/>
+      <c r="B163" s="130"/>
+      <c r="C163" s="131"/>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A165" s="4"/>
@@ -4671,6 +4580,27 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ed0ff079-217a-47d4-b7ec-91b316da1e03">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3042e918-aefc-4171-9d6c-c740f3c2ff7c" xsi:nil="true"/>
+    <Status xmlns="ed0ff079-217a-47d4-b7ec-91b316da1e03" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101001F1BD6F70B794D4A83A1A74C1C7FFB13" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a36ec311cb1a64ba9887f4cfe263bcf0">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="ed0ff079-217a-47d4-b7ec-91b316da1e03" xmlns:ns3="3042e918-aefc-4171-9d6c-c740f3c2ff7c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b5d2f1e144e455241c9e34cacdc13afb" ns2:_="" ns3:_="">
     <xsd:import namespace="ed0ff079-217a-47d4-b7ec-91b316da1e03"/>
@@ -4913,42 +4843,10 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ed0ff079-217a-47d4-b7ec-91b316da1e03">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="3042e918-aefc-4171-9d6c-c740f3c2ff7c" xsi:nil="true"/>
-    <Status xmlns="ed0ff079-217a-47d4-b7ec-91b316da1e03" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F2AA363C-5FFF-4389-992E-0B1456F9F257}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0627FB08-4574-4A0A-A2C4-FFFB20FF76D4}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="ed0ff079-217a-47d4-b7ec-91b316da1e03"/>
-    <ds:schemaRef ds:uri="3042e918-aefc-4171-9d6c-c740f3c2ff7c"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -4971,9 +4869,20 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0627FB08-4574-4A0A-A2C4-FFFB20FF76D4}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F2AA363C-5FFF-4389-992E-0B1456F9F257}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="ed0ff079-217a-47d4-b7ec-91b316da1e03"/>
+    <ds:schemaRef ds:uri="3042e918-aefc-4171-9d6c-c740f3c2ff7c"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/data/Conditions_Queries.xlsx
+++ b/data/Conditions_Queries.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GIS\Henrico\Henrico_Data_2026\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C53C885-3800-4FE2-A450-0562617A0C06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67409EFE-835F-4133-B342-F95B246190B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{35C825B9-898A-46C9-A18E-DC972BBDF846}"/>
   </bookViews>
@@ -1240,7 +1240,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="139">
+  <cellXfs count="127">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
@@ -1393,40 +1393,20 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="0" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="0" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="0" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="3" fontId="2" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -3452,7 +3432,7 @@
   <dimension ref="A1:C168"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="112.42578125" customWidth="1"/>
+    <col min="1" max="1" width="124.42578125" customWidth="1"/>
     <col min="2" max="2" width="25.28515625" customWidth="1"/>
     <col min="3" max="3" width="22.42578125" style="99" customWidth="1"/>
   </cols>
@@ -3756,8 +3736,8 @@
       <c r="A42" s="84" t="s">
         <v>93</v>
       </c>
-      <c r="B42" s="132"/>
-      <c r="C42" s="133" t="s">
+      <c r="B42" s="120"/>
+      <c r="C42" s="121" t="s">
         <v>8</v>
       </c>
     </row>
@@ -3765,15 +3745,15 @@
       <c r="A43" s="87" t="s">
         <v>94</v>
       </c>
-      <c r="B43" s="134"/>
-      <c r="C43" s="135"/>
+      <c r="B43" s="122"/>
+      <c r="C43" s="123"/>
     </row>
     <row r="44" spans="1:3" s="80" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="90" t="s">
         <v>95</v>
       </c>
-      <c r="B44" s="136"/>
-      <c r="C44" s="137"/>
+      <c r="B44" s="124"/>
+      <c r="C44" s="125"/>
     </row>
     <row r="45" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="51"/>
@@ -3865,696 +3845,696 @@
       <c r="C57" s="98"/>
     </row>
     <row r="58" spans="1:3" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A58" s="138" t="s">
+      <c r="A58" s="126" t="s">
         <v>17</v>
       </c>
       <c r="B58" s="106"/>
       <c r="C58" s="107"/>
     </row>
-    <row r="59" spans="1:3" s="114" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A59" s="111" t="s">
         <v>18</v>
       </c>
-      <c r="B59" s="112"/>
-      <c r="C59" s="113"/>
-    </row>
-    <row r="60" spans="1:3" s="114" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B59" s="6"/>
+      <c r="C59" s="112"/>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="84" t="s">
         <v>115</v>
       </c>
-      <c r="B60" s="115"/>
-      <c r="C60" s="116"/>
-    </row>
-    <row r="61" spans="1:3" s="114" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B60" s="85"/>
+      <c r="C60" s="101"/>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" s="87" t="s">
         <v>114</v>
       </c>
-      <c r="B61" s="117"/>
-      <c r="C61" s="118"/>
-    </row>
-    <row r="62" spans="1:3" s="114" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B61" s="88"/>
+      <c r="C61" s="96"/>
+    </row>
+    <row r="62" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A62" s="90" t="s">
         <v>116</v>
       </c>
-      <c r="B62" s="119"/>
-      <c r="C62" s="120"/>
-    </row>
-    <row r="63" spans="1:3" s="114" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B62" s="91"/>
+      <c r="C62" s="97"/>
+    </row>
+    <row r="63" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A63" s="41"/>
-      <c r="B63" s="121"/>
-      <c r="C63" s="122"/>
-    </row>
-    <row r="64" spans="1:3" s="114" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B63" s="42"/>
+      <c r="C63" s="102"/>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" s="84" t="s">
         <v>117</v>
       </c>
-      <c r="B64" s="115"/>
-      <c r="C64" s="116"/>
-    </row>
-    <row r="65" spans="1:3" s="114" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B64" s="85"/>
+      <c r="C64" s="101"/>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" s="87" t="s">
         <v>118</v>
       </c>
-      <c r="B65" s="117"/>
-      <c r="C65" s="118"/>
-    </row>
-    <row r="66" spans="1:3" s="114" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="123" t="s">
+      <c r="B65" s="88"/>
+      <c r="C65" s="96"/>
+    </row>
+    <row r="66" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="113" t="s">
         <v>119</v>
       </c>
-      <c r="B66" s="120"/>
-      <c r="C66" s="120"/>
-    </row>
-    <row r="67" spans="1:3" s="114" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B66" s="97"/>
+      <c r="C66" s="97"/>
+    </row>
+    <row r="67" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A67" s="41"/>
-      <c r="B67" s="121"/>
-      <c r="C67" s="122"/>
-    </row>
-    <row r="68" spans="1:3" s="114" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B67" s="42"/>
+      <c r="C67" s="102"/>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" s="84" t="s">
         <v>120</v>
       </c>
-      <c r="B68" s="115"/>
-      <c r="C68" s="116"/>
-    </row>
-    <row r="69" spans="1:3" s="114" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B68" s="85"/>
+      <c r="C68" s="101"/>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" s="87" t="s">
         <v>121</v>
       </c>
-      <c r="B69" s="117"/>
-      <c r="C69" s="118"/>
-    </row>
-    <row r="70" spans="1:3" s="114" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B69" s="88"/>
+      <c r="C69" s="96"/>
+    </row>
+    <row r="70" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A70" s="90" t="s">
         <v>122</v>
       </c>
-      <c r="B70" s="119"/>
-      <c r="C70" s="120"/>
-    </row>
-    <row r="71" spans="1:3" s="114" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="124"/>
-      <c r="B71" s="125"/>
-      <c r="C71" s="126"/>
-    </row>
-    <row r="72" spans="1:3" s="114" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="127" t="s">
-        <v>123</v>
-      </c>
-      <c r="B72" s="128"/>
-      <c r="C72" s="129"/>
-    </row>
-    <row r="73" spans="1:3" s="114" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B70" s="91"/>
+      <c r="C70" s="97"/>
+    </row>
+    <row r="71" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="114"/>
+      <c r="B71" s="115"/>
+      <c r="C71" s="116"/>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72" s="84" t="s">
+        <v>113</v>
+      </c>
+      <c r="B72" s="117"/>
+      <c r="C72" s="118"/>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" s="87" t="s">
-        <v>124</v>
-      </c>
-      <c r="B73" s="117"/>
-      <c r="C73" s="118"/>
-    </row>
-    <row r="74" spans="1:3" s="114" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>91</v>
+      </c>
+      <c r="B73" s="88"/>
+      <c r="C73" s="96"/>
+    </row>
+    <row r="74" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A74" s="90" t="s">
-        <v>125</v>
-      </c>
-      <c r="B74" s="119"/>
-      <c r="C74" s="120"/>
+        <v>92</v>
+      </c>
+      <c r="B74" s="91"/>
+      <c r="C74" s="97"/>
     </row>
     <row r="75" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A75" s="108"/>
       <c r="B75" s="109"/>
       <c r="C75" s="110"/>
     </row>
-    <row r="76" spans="1:3" s="114" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" s="84" t="s">
         <v>166</v>
       </c>
-      <c r="B76" s="115"/>
-      <c r="C76" s="116"/>
-    </row>
-    <row r="77" spans="1:3" s="114" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B76" s="85"/>
+      <c r="C76" s="101"/>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" s="87" t="s">
         <v>167</v>
       </c>
-      <c r="B77" s="117"/>
-      <c r="C77" s="118"/>
-    </row>
-    <row r="78" spans="1:3" s="114" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B77" s="88"/>
+      <c r="C77" s="96"/>
+    </row>
+    <row r="78" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A78" s="90" t="s">
         <v>168</v>
       </c>
-      <c r="B78" s="119"/>
-      <c r="C78" s="120"/>
-    </row>
-    <row r="79" spans="1:3" s="114" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B78" s="91"/>
+      <c r="C78" s="97"/>
+    </row>
+    <row r="79" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A79" s="71"/>
-      <c r="B79" s="130"/>
-      <c r="C79" s="131"/>
-    </row>
-    <row r="80" spans="1:3" s="114" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B79" s="68"/>
+      <c r="C79" s="119"/>
+    </row>
+    <row r="80" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A80" s="111" t="s">
         <v>19</v>
       </c>
-      <c r="B80" s="112"/>
-      <c r="C80" s="113"/>
-    </row>
-    <row r="81" spans="1:3" s="114" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B80" s="6"/>
+      <c r="C80" s="112"/>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" s="84" t="s">
         <v>115</v>
       </c>
-      <c r="B81" s="115"/>
-      <c r="C81" s="116"/>
-    </row>
-    <row r="82" spans="1:3" s="114" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B81" s="85"/>
+      <c r="C81" s="101"/>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" s="87" t="s">
         <v>114</v>
       </c>
-      <c r="B82" s="117"/>
-      <c r="C82" s="118"/>
-    </row>
-    <row r="83" spans="1:3" s="114" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B82" s="88"/>
+      <c r="C82" s="96"/>
+    </row>
+    <row r="83" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A83" s="90" t="s">
         <v>116</v>
       </c>
-      <c r="B83" s="119"/>
-      <c r="C83" s="120"/>
-    </row>
-    <row r="84" spans="1:3" s="114" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B83" s="91"/>
+      <c r="C83" s="97"/>
+    </row>
+    <row r="84" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A84" s="41"/>
-      <c r="B84" s="121"/>
-      <c r="C84" s="122"/>
-    </row>
-    <row r="85" spans="1:3" s="114" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B84" s="42"/>
+      <c r="C84" s="102"/>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" s="84" t="s">
         <v>117</v>
       </c>
-      <c r="B85" s="115"/>
-      <c r="C85" s="116"/>
-    </row>
-    <row r="86" spans="1:3" s="114" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B85" s="85"/>
+      <c r="C85" s="101"/>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" s="87" t="s">
         <v>118</v>
       </c>
-      <c r="B86" s="117"/>
-      <c r="C86" s="118"/>
-    </row>
-    <row r="87" spans="1:3" s="114" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="123" t="s">
+      <c r="B86" s="88"/>
+      <c r="C86" s="96"/>
+    </row>
+    <row r="87" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A87" s="113" t="s">
         <v>119</v>
       </c>
-      <c r="B87" s="120"/>
-      <c r="C87" s="120"/>
-    </row>
-    <row r="88" spans="1:3" s="114" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B87" s="97"/>
+      <c r="C87" s="97"/>
+    </row>
+    <row r="88" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A88" s="41"/>
-      <c r="B88" s="121"/>
-      <c r="C88" s="122"/>
-    </row>
-    <row r="89" spans="1:3" s="114" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B88" s="42"/>
+      <c r="C88" s="102"/>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" s="84" t="s">
         <v>120</v>
       </c>
-      <c r="B89" s="115"/>
-      <c r="C89" s="116"/>
-    </row>
-    <row r="90" spans="1:3" s="114" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B89" s="85"/>
+      <c r="C89" s="101"/>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" s="87" t="s">
         <v>121</v>
       </c>
-      <c r="B90" s="117"/>
-      <c r="C90" s="118"/>
-    </row>
-    <row r="91" spans="1:3" s="114" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B90" s="88"/>
+      <c r="C90" s="96"/>
+    </row>
+    <row r="91" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A91" s="90" t="s">
         <v>122</v>
       </c>
-      <c r="B91" s="119"/>
-      <c r="C91" s="120"/>
-    </row>
-    <row r="92" spans="1:3" s="114" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="124"/>
-      <c r="B92" s="125"/>
-      <c r="C92" s="126"/>
-    </row>
-    <row r="93" spans="1:3" s="114" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="127" t="s">
-        <v>123</v>
-      </c>
-      <c r="B93" s="128"/>
-      <c r="C93" s="129"/>
-    </row>
-    <row r="94" spans="1:3" s="114" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B91" s="91"/>
+      <c r="C91" s="97"/>
+    </row>
+    <row r="92" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A92" s="114"/>
+      <c r="B92" s="115"/>
+      <c r="C92" s="116"/>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A93" s="84" t="s">
+        <v>113</v>
+      </c>
+      <c r="B93" s="117"/>
+      <c r="C93" s="118"/>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" s="87" t="s">
-        <v>124</v>
-      </c>
-      <c r="B94" s="117"/>
-      <c r="C94" s="118"/>
-    </row>
-    <row r="95" spans="1:3" s="114" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>91</v>
+      </c>
+      <c r="B94" s="88"/>
+      <c r="C94" s="96"/>
+    </row>
+    <row r="95" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A95" s="90" t="s">
-        <v>125</v>
-      </c>
-      <c r="B95" s="119"/>
-      <c r="C95" s="120"/>
-    </row>
-    <row r="96" spans="1:3" s="114" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>92</v>
+      </c>
+      <c r="B95" s="91"/>
+      <c r="C95" s="97"/>
+    </row>
+    <row r="96" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A96" s="41"/>
-      <c r="B96" s="121"/>
-      <c r="C96" s="122"/>
-    </row>
-    <row r="97" spans="1:3" s="114" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B96" s="42"/>
+      <c r="C96" s="102"/>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" s="84" t="s">
         <v>166</v>
       </c>
-      <c r="B97" s="115"/>
-      <c r="C97" s="116"/>
-    </row>
-    <row r="98" spans="1:3" s="114" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B97" s="85"/>
+      <c r="C97" s="101"/>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" s="87" t="s">
         <v>167</v>
       </c>
-      <c r="B98" s="117"/>
-      <c r="C98" s="118"/>
-    </row>
-    <row r="99" spans="1:3" s="114" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B98" s="88"/>
+      <c r="C98" s="96"/>
+    </row>
+    <row r="99" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A99" s="90" t="s">
         <v>168</v>
       </c>
-      <c r="B99" s="119"/>
-      <c r="C99" s="120"/>
-    </row>
-    <row r="100" spans="1:3" s="114" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B99" s="91"/>
+      <c r="C99" s="97"/>
+    </row>
+    <row r="100" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A100" s="71"/>
-      <c r="B100" s="130"/>
-      <c r="C100" s="131"/>
-    </row>
-    <row r="101" spans="1:3" s="114" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B100" s="68"/>
+      <c r="C100" s="119"/>
+    </row>
+    <row r="101" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A101" s="111" t="s">
         <v>20</v>
       </c>
-      <c r="B101" s="112"/>
-      <c r="C101" s="113"/>
-    </row>
-    <row r="102" spans="1:3" s="114" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B101" s="6"/>
+      <c r="C101" s="112"/>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102" s="84" t="s">
         <v>115</v>
       </c>
-      <c r="B102" s="115"/>
-      <c r="C102" s="116"/>
-    </row>
-    <row r="103" spans="1:3" s="114" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B102" s="85"/>
+      <c r="C102" s="101"/>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" s="87" t="s">
         <v>114</v>
       </c>
-      <c r="B103" s="117"/>
-      <c r="C103" s="118"/>
-    </row>
-    <row r="104" spans="1:3" s="114" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B103" s="88"/>
+      <c r="C103" s="96"/>
+    </row>
+    <row r="104" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A104" s="90" t="s">
         <v>116</v>
       </c>
-      <c r="B104" s="119"/>
-      <c r="C104" s="120"/>
-    </row>
-    <row r="105" spans="1:3" s="114" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B104" s="91"/>
+      <c r="C104" s="97"/>
+    </row>
+    <row r="105" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A105" s="41"/>
-      <c r="B105" s="121"/>
-      <c r="C105" s="122"/>
-    </row>
-    <row r="106" spans="1:3" s="114" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B105" s="42"/>
+      <c r="C105" s="102"/>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106" s="84" t="s">
         <v>117</v>
       </c>
-      <c r="B106" s="115"/>
-      <c r="C106" s="116"/>
-    </row>
-    <row r="107" spans="1:3" s="114" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B106" s="85"/>
+      <c r="C106" s="101"/>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107" s="87" t="s">
         <v>118</v>
       </c>
-      <c r="B107" s="117"/>
-      <c r="C107" s="118"/>
-    </row>
-    <row r="108" spans="1:3" s="114" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A108" s="123" t="s">
+      <c r="B107" s="88"/>
+      <c r="C107" s="96"/>
+    </row>
+    <row r="108" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A108" s="113" t="s">
         <v>119</v>
       </c>
-      <c r="B108" s="120"/>
-      <c r="C108" s="120"/>
-    </row>
-    <row r="109" spans="1:3" s="114" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B108" s="97"/>
+      <c r="C108" s="97"/>
+    </row>
+    <row r="109" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A109" s="41"/>
-      <c r="B109" s="121"/>
-      <c r="C109" s="122"/>
-    </row>
-    <row r="110" spans="1:3" s="114" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B109" s="42"/>
+      <c r="C109" s="102"/>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A110" s="84" t="s">
         <v>120</v>
       </c>
-      <c r="B110" s="115"/>
-      <c r="C110" s="116"/>
-    </row>
-    <row r="111" spans="1:3" s="114" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B110" s="85"/>
+      <c r="C110" s="101"/>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A111" s="87" t="s">
         <v>121</v>
       </c>
-      <c r="B111" s="117"/>
-      <c r="C111" s="118"/>
-    </row>
-    <row r="112" spans="1:3" s="114" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B111" s="88"/>
+      <c r="C111" s="96"/>
+    </row>
+    <row r="112" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A112" s="90" t="s">
         <v>122</v>
       </c>
-      <c r="B112" s="119"/>
-      <c r="C112" s="120"/>
-    </row>
-    <row r="113" spans="1:3" s="114" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A113" s="124"/>
-      <c r="B113" s="125"/>
-      <c r="C113" s="126"/>
-    </row>
-    <row r="114" spans="1:3" s="114" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A114" s="127" t="s">
-        <v>123</v>
-      </c>
-      <c r="B114" s="128"/>
-      <c r="C114" s="129"/>
-    </row>
-    <row r="115" spans="1:3" s="114" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B112" s="91"/>
+      <c r="C112" s="97"/>
+    </row>
+    <row r="113" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A113" s="114"/>
+      <c r="B113" s="115"/>
+      <c r="C113" s="116"/>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A114" s="84" t="s">
+        <v>113</v>
+      </c>
+      <c r="B114" s="117"/>
+      <c r="C114" s="118"/>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A115" s="87" t="s">
-        <v>124</v>
-      </c>
-      <c r="B115" s="117"/>
-      <c r="C115" s="118"/>
-    </row>
-    <row r="116" spans="1:3" s="114" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>91</v>
+      </c>
+      <c r="B115" s="88"/>
+      <c r="C115" s="96"/>
+    </row>
+    <row r="116" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A116" s="90" t="s">
-        <v>125</v>
-      </c>
-      <c r="B116" s="119"/>
-      <c r="C116" s="120"/>
-    </row>
-    <row r="117" spans="1:3" s="114" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>92</v>
+      </c>
+      <c r="B116" s="91"/>
+      <c r="C116" s="97"/>
+    </row>
+    <row r="117" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A117" s="41"/>
-      <c r="B117" s="121"/>
-      <c r="C117" s="122"/>
-    </row>
-    <row r="118" spans="1:3" s="114" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B117" s="42"/>
+      <c r="C117" s="102"/>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A118" s="84" t="s">
         <v>166</v>
       </c>
-      <c r="B118" s="115"/>
-      <c r="C118" s="116"/>
-    </row>
-    <row r="119" spans="1:3" s="114" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B118" s="85"/>
+      <c r="C118" s="101"/>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A119" s="87" t="s">
         <v>167</v>
       </c>
-      <c r="B119" s="117"/>
-      <c r="C119" s="118"/>
-    </row>
-    <row r="120" spans="1:3" s="114" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B119" s="88"/>
+      <c r="C119" s="96"/>
+    </row>
+    <row r="120" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A120" s="90" t="s">
         <v>168</v>
       </c>
-      <c r="B120" s="119"/>
-      <c r="C120" s="120"/>
-    </row>
-    <row r="121" spans="1:3" s="114" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B120" s="91"/>
+      <c r="C120" s="97"/>
+    </row>
+    <row r="121" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A121" s="71"/>
-      <c r="B121" s="130"/>
-      <c r="C121" s="131"/>
-    </row>
-    <row r="122" spans="1:3" s="114" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B121" s="68"/>
+      <c r="C121" s="119"/>
+    </row>
+    <row r="122" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A122" s="111" t="s">
         <v>21</v>
       </c>
-      <c r="B122" s="112"/>
-      <c r="C122" s="113"/>
-    </row>
-    <row r="123" spans="1:3" s="114" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B122" s="6"/>
+      <c r="C122" s="112"/>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A123" s="84" t="s">
         <v>115</v>
       </c>
-      <c r="B123" s="115"/>
-      <c r="C123" s="116"/>
-    </row>
-    <row r="124" spans="1:3" s="114" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B123" s="85"/>
+      <c r="C123" s="101"/>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A124" s="87" t="s">
         <v>114</v>
       </c>
-      <c r="B124" s="117"/>
-      <c r="C124" s="118"/>
-    </row>
-    <row r="125" spans="1:3" s="114" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B124" s="88"/>
+      <c r="C124" s="96"/>
+    </row>
+    <row r="125" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A125" s="90" t="s">
         <v>116</v>
       </c>
-      <c r="B125" s="119"/>
-      <c r="C125" s="120"/>
-    </row>
-    <row r="126" spans="1:3" s="114" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B125" s="91"/>
+      <c r="C125" s="97"/>
+    </row>
+    <row r="126" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A126" s="41"/>
-      <c r="B126" s="121"/>
-      <c r="C126" s="122"/>
-    </row>
-    <row r="127" spans="1:3" s="114" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B126" s="42"/>
+      <c r="C126" s="102"/>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A127" s="84" t="s">
         <v>117</v>
       </c>
-      <c r="B127" s="115"/>
-      <c r="C127" s="116"/>
-    </row>
-    <row r="128" spans="1:3" s="114" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B127" s="85"/>
+      <c r="C127" s="101"/>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A128" s="87" t="s">
         <v>118</v>
       </c>
-      <c r="B128" s="117"/>
-      <c r="C128" s="118"/>
-    </row>
-    <row r="129" spans="1:3" s="114" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A129" s="123" t="s">
+      <c r="B128" s="88"/>
+      <c r="C128" s="96"/>
+    </row>
+    <row r="129" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A129" s="113" t="s">
         <v>119</v>
       </c>
-      <c r="B129" s="120"/>
-      <c r="C129" s="120"/>
-    </row>
-    <row r="130" spans="1:3" s="114" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B129" s="97"/>
+      <c r="C129" s="97"/>
+    </row>
+    <row r="130" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A130" s="41"/>
-      <c r="B130" s="121"/>
-      <c r="C130" s="122"/>
-    </row>
-    <row r="131" spans="1:3" s="114" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B130" s="42"/>
+      <c r="C130" s="102"/>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A131" s="84" t="s">
         <v>120</v>
       </c>
-      <c r="B131" s="115"/>
-      <c r="C131" s="116"/>
-    </row>
-    <row r="132" spans="1:3" s="114" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B131" s="85"/>
+      <c r="C131" s="101"/>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A132" s="87" t="s">
         <v>121</v>
       </c>
-      <c r="B132" s="117"/>
-      <c r="C132" s="118"/>
-    </row>
-    <row r="133" spans="1:3" s="114" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B132" s="88"/>
+      <c r="C132" s="96"/>
+    </row>
+    <row r="133" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A133" s="90" t="s">
         <v>122</v>
       </c>
-      <c r="B133" s="119"/>
-      <c r="C133" s="120"/>
-    </row>
-    <row r="134" spans="1:3" s="114" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A134" s="124"/>
-      <c r="B134" s="125"/>
-      <c r="C134" s="126"/>
-    </row>
-    <row r="135" spans="1:3" s="114" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A135" s="127" t="s">
-        <v>123</v>
-      </c>
-      <c r="B135" s="128"/>
-      <c r="C135" s="129"/>
-    </row>
-    <row r="136" spans="1:3" s="114" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B133" s="91"/>
+      <c r="C133" s="97"/>
+    </row>
+    <row r="134" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A134" s="114"/>
+      <c r="B134" s="115"/>
+      <c r="C134" s="116"/>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A135" s="84" t="s">
+        <v>113</v>
+      </c>
+      <c r="B135" s="117"/>
+      <c r="C135" s="118"/>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A136" s="87" t="s">
-        <v>124</v>
-      </c>
-      <c r="B136" s="117"/>
-      <c r="C136" s="118"/>
-    </row>
-    <row r="137" spans="1:3" s="114" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>91</v>
+      </c>
+      <c r="B136" s="88"/>
+      <c r="C136" s="96"/>
+    </row>
+    <row r="137" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A137" s="90" t="s">
-        <v>125</v>
-      </c>
-      <c r="B137" s="119"/>
-      <c r="C137" s="120"/>
-    </row>
-    <row r="138" spans="1:3" s="114" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>92</v>
+      </c>
+      <c r="B137" s="91"/>
+      <c r="C137" s="97"/>
+    </row>
+    <row r="138" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A138" s="41"/>
-      <c r="B138" s="121"/>
-      <c r="C138" s="122"/>
-    </row>
-    <row r="139" spans="1:3" s="114" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B138" s="42"/>
+      <c r="C138" s="102"/>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A139" s="84" t="s">
         <v>166</v>
       </c>
-      <c r="B139" s="115"/>
-      <c r="C139" s="116"/>
-    </row>
-    <row r="140" spans="1:3" s="114" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B139" s="85"/>
+      <c r="C139" s="101"/>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A140" s="87" t="s">
         <v>167</v>
       </c>
-      <c r="B140" s="117"/>
-      <c r="C140" s="118"/>
-    </row>
-    <row r="141" spans="1:3" s="114" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B140" s="88"/>
+      <c r="C140" s="96"/>
+    </row>
+    <row r="141" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A141" s="90" t="s">
         <v>168</v>
       </c>
-      <c r="B141" s="119"/>
-      <c r="C141" s="120"/>
-    </row>
-    <row r="142" spans="1:3" s="114" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B141" s="91"/>
+      <c r="C141" s="97"/>
+    </row>
+    <row r="142" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A142" s="71"/>
-      <c r="B142" s="130"/>
-      <c r="C142" s="131"/>
-    </row>
-    <row r="143" spans="1:3" s="114" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B142" s="68"/>
+      <c r="C142" s="119"/>
+    </row>
+    <row r="143" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A143" s="111" t="s">
         <v>22</v>
       </c>
-      <c r="B143" s="112"/>
-      <c r="C143" s="113"/>
-    </row>
-    <row r="144" spans="1:3" s="114" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B143" s="6"/>
+      <c r="C143" s="112"/>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A144" s="84" t="s">
         <v>115</v>
       </c>
-      <c r="B144" s="115"/>
-      <c r="C144" s="116"/>
-    </row>
-    <row r="145" spans="1:3" s="114" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B144" s="85"/>
+      <c r="C144" s="101"/>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A145" s="87" t="s">
         <v>114</v>
       </c>
-      <c r="B145" s="117"/>
-      <c r="C145" s="118"/>
-    </row>
-    <row r="146" spans="1:3" s="114" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B145" s="88"/>
+      <c r="C145" s="96"/>
+    </row>
+    <row r="146" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A146" s="90" t="s">
         <v>116</v>
       </c>
-      <c r="B146" s="119"/>
-      <c r="C146" s="120"/>
-    </row>
-    <row r="147" spans="1:3" s="114" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B146" s="91"/>
+      <c r="C146" s="97"/>
+    </row>
+    <row r="147" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A147" s="41"/>
-      <c r="B147" s="121"/>
-      <c r="C147" s="122"/>
-    </row>
-    <row r="148" spans="1:3" s="114" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B147" s="42"/>
+      <c r="C147" s="102"/>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A148" s="84" t="s">
         <v>117</v>
       </c>
-      <c r="B148" s="115"/>
-      <c r="C148" s="116"/>
-    </row>
-    <row r="149" spans="1:3" s="114" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B148" s="85"/>
+      <c r="C148" s="101"/>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A149" s="87" t="s">
         <v>118</v>
       </c>
-      <c r="B149" s="117"/>
-      <c r="C149" s="118"/>
-    </row>
-    <row r="150" spans="1:3" s="114" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A150" s="123" t="s">
+      <c r="B149" s="88"/>
+      <c r="C149" s="96"/>
+    </row>
+    <row r="150" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A150" s="113" t="s">
         <v>119</v>
       </c>
-      <c r="B150" s="120"/>
-      <c r="C150" s="120"/>
-    </row>
-    <row r="151" spans="1:3" s="114" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B150" s="97"/>
+      <c r="C150" s="97"/>
+    </row>
+    <row r="151" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A151" s="41"/>
-      <c r="B151" s="121"/>
-      <c r="C151" s="122"/>
-    </row>
-    <row r="152" spans="1:3" s="114" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B151" s="42"/>
+      <c r="C151" s="102"/>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A152" s="84" t="s">
         <v>120</v>
       </c>
-      <c r="B152" s="115"/>
-      <c r="C152" s="116"/>
-    </row>
-    <row r="153" spans="1:3" s="114" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B152" s="85"/>
+      <c r="C152" s="101"/>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A153" s="87" t="s">
         <v>121</v>
       </c>
-      <c r="B153" s="117"/>
-      <c r="C153" s="118"/>
-    </row>
-    <row r="154" spans="1:3" s="114" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B153" s="88"/>
+      <c r="C153" s="96"/>
+    </row>
+    <row r="154" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A154" s="90" t="s">
         <v>122</v>
       </c>
-      <c r="B154" s="119"/>
-      <c r="C154" s="120"/>
-    </row>
-    <row r="155" spans="1:3" s="114" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A155" s="124"/>
-      <c r="B155" s="125"/>
-      <c r="C155" s="126"/>
-    </row>
-    <row r="156" spans="1:3" s="114" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A156" s="127" t="s">
-        <v>123</v>
-      </c>
-      <c r="B156" s="128"/>
-      <c r="C156" s="129"/>
-    </row>
-    <row r="157" spans="1:3" s="114" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B154" s="91"/>
+      <c r="C154" s="97"/>
+    </row>
+    <row r="155" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A155" s="114"/>
+      <c r="B155" s="115"/>
+      <c r="C155" s="116"/>
+    </row>
+    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A156" s="84" t="s">
+        <v>113</v>
+      </c>
+      <c r="B156" s="117"/>
+      <c r="C156" s="118"/>
+    </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A157" s="87" t="s">
-        <v>124</v>
-      </c>
-      <c r="B157" s="117"/>
-      <c r="C157" s="118"/>
-    </row>
-    <row r="158" spans="1:3" s="114" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>91</v>
+      </c>
+      <c r="B157" s="88"/>
+      <c r="C157" s="96"/>
+    </row>
+    <row r="158" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A158" s="90" t="s">
-        <v>125</v>
-      </c>
-      <c r="B158" s="119"/>
-      <c r="C158" s="120"/>
-    </row>
-    <row r="159" spans="1:3" s="114" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>92</v>
+      </c>
+      <c r="B158" s="91"/>
+      <c r="C158" s="97"/>
+    </row>
+    <row r="159" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A159" s="41"/>
-      <c r="B159" s="121"/>
-      <c r="C159" s="122"/>
-    </row>
-    <row r="160" spans="1:3" s="114" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B159" s="42"/>
+      <c r="C159" s="102"/>
+    </row>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A160" s="84" t="s">
         <v>166</v>
       </c>
-      <c r="B160" s="115"/>
-      <c r="C160" s="116"/>
-    </row>
-    <row r="161" spans="1:3" s="114" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B160" s="85"/>
+      <c r="C160" s="101"/>
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A161" s="87" t="s">
         <v>167</v>
       </c>
-      <c r="B161" s="117"/>
-      <c r="C161" s="118"/>
-    </row>
-    <row r="162" spans="1:3" s="114" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B161" s="88"/>
+      <c r="C161" s="96"/>
+    </row>
+    <row r="162" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A162" s="90" t="s">
         <v>168</v>
       </c>
-      <c r="B162" s="119"/>
-      <c r="C162" s="120"/>
-    </row>
-    <row r="163" spans="1:3" s="114" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B162" s="91"/>
+      <c r="C162" s="97"/>
+    </row>
+    <row r="163" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A163" s="71"/>
-      <c r="B163" s="130"/>
-      <c r="C163" s="131"/>
+      <c r="B163" s="68"/>
+      <c r="C163" s="119"/>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A165" s="4"/>
@@ -4580,27 +4560,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ed0ff079-217a-47d4-b7ec-91b316da1e03">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="3042e918-aefc-4171-9d6c-c740f3c2ff7c" xsi:nil="true"/>
-    <Status xmlns="ed0ff079-217a-47d4-b7ec-91b316da1e03" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101001F1BD6F70B794D4A83A1A74C1C7FFB13" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a36ec311cb1a64ba9887f4cfe263bcf0">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="ed0ff079-217a-47d4-b7ec-91b316da1e03" xmlns:ns3="3042e918-aefc-4171-9d6c-c740f3c2ff7c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b5d2f1e144e455241c9e34cacdc13afb" ns2:_="" ns3:_="">
     <xsd:import namespace="ed0ff079-217a-47d4-b7ec-91b316da1e03"/>
@@ -4843,10 +4802,42 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ed0ff079-217a-47d4-b7ec-91b316da1e03">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3042e918-aefc-4171-9d6c-c740f3c2ff7c" xsi:nil="true"/>
+    <Status xmlns="ed0ff079-217a-47d4-b7ec-91b316da1e03" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0627FB08-4574-4A0A-A2C4-FFFB20FF76D4}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F2AA363C-5FFF-4389-992E-0B1456F9F257}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="ed0ff079-217a-47d4-b7ec-91b316da1e03"/>
+    <ds:schemaRef ds:uri="3042e918-aefc-4171-9d6c-c740f3c2ff7c"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -4869,20 +4860,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F2AA363C-5FFF-4389-992E-0B1456F9F257}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0627FB08-4574-4A0A-A2C4-FFFB20FF76D4}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="ed0ff079-217a-47d4-b7ec-91b316da1e03"/>
-    <ds:schemaRef ds:uri="3042e918-aefc-4171-9d6c-c740f3c2ff7c"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
